--- a/Ressources/Dl/TableauSynthese.xlsx
+++ b/Ressources/Dl/TableauSynthese.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\delau\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6637D84F-092B-476A-BC34-DE648706B5BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EC08926-E76B-484C-9501-3EB6BE2C4698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+  <si>
+    <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
+  </si>
   <si>
     <t>SESSION 2025</t>
   </si>
@@ -40,7 +43,7 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
       </rPr>
-      <t xml:space="preserve">NOM et prénom :      </t>
+      <t xml:space="preserve">NOM et prénom :   </t>
     </r>
     <r>
       <rPr>
@@ -54,7 +57,25 @@
     </r>
   </si>
   <si>
-    <t>N° candidat :    02249595239</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">N° candidat :    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="18"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>022495955239</t>
+    </r>
   </si>
   <si>
     <r>
@@ -64,7 +85,7 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
       </rPr>
-      <t xml:space="preserve">Centre de formation :     </t>
+      <t xml:space="preserve">Centre de formation :   </t>
     </r>
     <r>
       <rPr>
@@ -84,7 +105,25 @@
     <t>▢ SISR</t>
   </si>
   <si>
-    <t>Adresse URL du portfolio :    https://unskal.github.io/Portfolio</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">Adresse URL du portfolio :  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="18"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve"> https://unskal.github.io/Portfolio</t>
+    </r>
   </si>
   <si>
     <t>Compétences mises en œuvre
@@ -157,7 +196,16 @@
     <t>Application Desktop : Unsflix</t>
   </si>
   <si>
-    <t>01/01/25 - 01/06/25</t>
+    <t>01/01/2025 - 01/06/2025</t>
+  </si>
+  <si>
+    <t>Conception d'un portfolio</t>
+  </si>
+  <si>
+    <t>01/01/2026 - 01/06/2026</t>
+  </si>
+  <si>
+    <t>Conception d'un morpion</t>
   </si>
   <si>
     <t>Réalisations en milieu professionnel en cours de première année</t>
@@ -166,7 +214,7 @@
     <t>Site internet : Brocante des continents</t>
   </si>
   <si>
-    <t>12/05/25 au 13/06/25</t>
+    <t>12/05/2025 au 13/06/2025</t>
   </si>
   <si>
     <t>Réalisations en milieu professionnel en cours de seconde année</t>
@@ -175,7 +223,7 @@
     <t>Site internet : Happy Feet Bien-être</t>
   </si>
   <si>
-    <t>05/01/26 au 14/02/26</t>
+    <t>05/01/2026 au 14/02/2026</t>
   </si>
   <si>
     <t>[X] SLAM</t>
@@ -185,7 +233,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="45" x14ac:knownFonts="1">
+  <fonts count="48" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color indexed="8"/>
@@ -252,6 +300,10 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
       <name val="Calibri"/>
@@ -339,6 +391,14 @@
     <font>
       <b/>
       <sz val="14"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -765,7 +825,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -773,56 +833,68 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="17" fontId="28" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -830,26 +902,34 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1193,22 +1273,24 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.796875" defaultRowHeight="33" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="72.296875" customWidth="1"/>
-    <col min="2" max="2" width="27.09765625" customWidth="1"/>
+    <col min="2" max="2" width="30.3984375" customWidth="1"/>
     <col min="3" max="8" width="20.69921875" customWidth="1"/>
     <col min="9" max="26" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="25"/>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="25" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="26"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="28"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
@@ -1229,16 +1311,16 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="53.1" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="25" t="s">
-        <v>1</v>
+      <c r="A2" s="27" t="s">
+        <v>2</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -1259,18 +1341,18 @@
       <c r="Z2" s="2"/>
     </row>
     <row r="3" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="30" t="s">
+      <c r="A3" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="28"/>
-      <c r="H3" s="31"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="30"/>
+      <c r="H3" s="33"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="1"/>
@@ -1291,24 +1373,24 @@
       <c r="Z3" s="2"/>
     </row>
     <row r="4" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="32" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="3" t="s">
+      <c r="A4" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="44" t="s">
-        <v>32</v>
+      <c r="G4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="48" t="s">
+        <v>36</v>
       </c>
       <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
+      <c r="J4" s="5"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
@@ -1327,16 +1409,16 @@
       <c r="Z4" s="2"/>
     </row>
     <row r="5" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="35" t="s">
-        <v>7</v>
+      <c r="A5" s="37" t="s">
+        <v>8</v>
       </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="37"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="39"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -1357,29 +1439,29 @@
       <c r="Z5" s="2"/>
     </row>
     <row r="6" spans="1:26" ht="102" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="38" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="40" t="s">
+      <c r="A6" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="B6" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="F6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>15</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
@@ -1401,25 +1483,25 @@
       <c r="Z6" s="2"/>
     </row>
     <row r="7" spans="1:26" ht="336.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="39"/>
-      <c r="B7" s="41"/>
-      <c r="C7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="7" t="s">
+      <c r="A7" s="41"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="E7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="F7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="G7" s="8" t="s">
         <v>21</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>22</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -1439,20 +1521,20 @@
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
       <c r="Z7" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="29"/>
+    </row>
+    <row r="8" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="31"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -1473,18 +1555,18 @@
       <c r="Z8" s="1"/>
     </row>
     <row r="9" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="10" t="s">
+      <c r="A9" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="14"/>
+      <c r="B9" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="12"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="15"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -1505,13 +1587,17 @@
       <c r="Z9" s="1"/>
     </row>
     <row r="10" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="9"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
+      <c r="A10" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
       <c r="H10" s="15"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -1533,14 +1619,18 @@
       <c r="Z10" s="1"/>
     </row>
     <row r="11" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="9"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="15"/>
+      <c r="A11" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="26">
+        <v>45658</v>
+      </c>
+      <c r="C11" s="14"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="16"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -1561,14 +1651,14 @@
       <c r="Z11" s="1"/>
     </row>
     <row r="12" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="9"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="15"/>
+      <c r="A12" s="10"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="16"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -1589,14 +1679,14 @@
       <c r="Z12" s="1"/>
     </row>
     <row r="13" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="9"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="15"/>
+      <c r="A13" s="10"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="16"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -1617,14 +1707,14 @@
       <c r="Z13" s="1"/>
     </row>
     <row r="14" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="9"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="15"/>
+      <c r="A14" s="10"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="16"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -1645,14 +1735,14 @@
       <c r="Z14" s="1"/>
     </row>
     <row r="15" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="9"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="15"/>
+      <c r="A15" s="10"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="16"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -1673,14 +1763,14 @@
       <c r="Z15" s="1"/>
     </row>
     <row r="16" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="9"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="15"/>
+      <c r="A16" s="10"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="16"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -1701,14 +1791,14 @@
       <c r="Z16" s="1"/>
     </row>
     <row r="17" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="9"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="15"/>
+      <c r="A17" s="10"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="16"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -1729,14 +1819,14 @@
       <c r="Z17" s="1"/>
     </row>
     <row r="18" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="9"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="15"/>
+      <c r="A18" s="10"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="16"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -1757,16 +1847,16 @@
       <c r="Z18" s="1"/>
     </row>
     <row r="19" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="43" t="s">
-        <v>26</v>
+      <c r="A19" s="45" t="s">
+        <v>30</v>
       </c>
-      <c r="B19" s="33"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="34"/>
+      <c r="B19" s="46"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="46"/>
+      <c r="H19" s="47"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -1787,18 +1877,18 @@
       <c r="Z19" s="1"/>
     </row>
     <row r="20" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="9" t="s">
-        <v>27</v>
+      <c r="A20" s="10" t="s">
+        <v>31</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>28</v>
+      <c r="B20" s="11" t="s">
+        <v>32</v>
       </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="15"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="16"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -1819,14 +1909,14 @@
       <c r="Z20" s="1"/>
     </row>
     <row r="21" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="9"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="15"/>
+      <c r="A21" s="10"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="16"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -1847,14 +1937,14 @@
       <c r="Z21" s="1"/>
     </row>
     <row r="22" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="9"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="15"/>
+      <c r="A22" s="10"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="16"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -1875,14 +1965,14 @@
       <c r="Z22" s="1"/>
     </row>
     <row r="23" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="9"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="15"/>
+      <c r="A23" s="10"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="16"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
@@ -1903,14 +1993,14 @@
       <c r="Z23" s="1"/>
     </row>
     <row r="24" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="9"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="15"/>
+      <c r="A24" s="10"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="16"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
@@ -1931,14 +2021,14 @@
       <c r="Z24" s="1"/>
     </row>
     <row r="25" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="9"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="15"/>
+      <c r="A25" s="10"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="16"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
@@ -1959,14 +2049,14 @@
       <c r="Z25" s="1"/>
     </row>
     <row r="26" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="9"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="15"/>
+      <c r="A26" s="10"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="16"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
@@ -1987,16 +2077,16 @@
       <c r="Z26" s="1"/>
     </row>
     <row r="27" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="43" t="s">
-        <v>29</v>
+      <c r="A27" s="45" t="s">
+        <v>33</v>
       </c>
-      <c r="B27" s="33"/>
-      <c r="C27" s="33"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="34"/>
+      <c r="B27" s="46"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="47"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
@@ -2017,18 +2107,18 @@
       <c r="Z27" s="1"/>
     </row>
     <row r="28" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="9" t="s">
-        <v>30</v>
+      <c r="A28" s="10" t="s">
+        <v>34</v>
       </c>
-      <c r="B28" s="17" t="s">
-        <v>31</v>
+      <c r="B28" s="18" t="s">
+        <v>35</v>
       </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="15"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="16"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
@@ -2049,14 +2139,14 @@
       <c r="Z28" s="1"/>
     </row>
     <row r="29" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="9"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="15"/>
+      <c r="A29" s="10"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="16"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
@@ -2077,14 +2167,14 @@
       <c r="Z29" s="1"/>
     </row>
     <row r="30" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="9"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="15"/>
+      <c r="A30" s="10"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="16"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
@@ -2105,14 +2195,14 @@
       <c r="Z30" s="1"/>
     </row>
     <row r="31" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="9"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="15"/>
+      <c r="A31" s="10"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="16"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
@@ -2133,14 +2223,14 @@
       <c r="Z31" s="1"/>
     </row>
     <row r="32" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="9"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="15"/>
+      <c r="A32" s="10"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="16"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
@@ -2161,14 +2251,14 @@
       <c r="Z32" s="1"/>
     </row>
     <row r="33" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="9"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="15"/>
+      <c r="A33" s="10"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="16"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
@@ -2189,14 +2279,14 @@
       <c r="Z33" s="1"/>
     </row>
     <row r="34" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="18"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="21"/>
+      <c r="A34" s="19"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="22"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
@@ -2217,14 +2307,14 @@
       <c r="Z34" s="1"/>
     </row>
     <row r="35" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="22"/>
-      <c r="B35" s="23"/>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="24"/>
+      <c r="A35" s="23"/>
+      <c r="B35" s="24"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -2244,7 +2334,7 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
-    <row r="36" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -2272,7 +2362,7 @@
       <c r="Y36" s="2"/>
       <c r="Z36" s="2"/>
     </row>
-    <row r="37" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2300,7 +2390,7 @@
       <c r="Y37" s="2"/>
       <c r="Z37" s="2"/>
     </row>
-    <row r="38" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2328,7 +2418,7 @@
       <c r="Y38" s="2"/>
       <c r="Z38" s="2"/>
     </row>
-    <row r="39" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2356,7 +2446,7 @@
       <c r="Y39" s="2"/>
       <c r="Z39" s="2"/>
     </row>
-    <row r="40" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -2384,7 +2474,7 @@
       <c r="Y40" s="2"/>
       <c r="Z40" s="2"/>
     </row>
-    <row r="41" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -2412,7 +2502,7 @@
       <c r="Y41" s="2"/>
       <c r="Z41" s="2"/>
     </row>
-    <row r="42" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -2440,7 +2530,7 @@
       <c r="Y42" s="2"/>
       <c r="Z42" s="2"/>
     </row>
-    <row r="43" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -2468,7 +2558,7 @@
       <c r="Y43" s="2"/>
       <c r="Z43" s="2"/>
     </row>
-    <row r="44" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -2496,7 +2586,7 @@
       <c r="Y44" s="2"/>
       <c r="Z44" s="2"/>
     </row>
-    <row r="45" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -2524,7 +2614,7 @@
       <c r="Y45" s="2"/>
       <c r="Z45" s="2"/>
     </row>
-    <row r="46" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -2552,7 +2642,7 @@
       <c r="Y46" s="2"/>
       <c r="Z46" s="2"/>
     </row>
-    <row r="47" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -2580,7 +2670,7 @@
       <c r="Y47" s="2"/>
       <c r="Z47" s="2"/>
     </row>
-    <row r="48" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -2608,7 +2698,7 @@
       <c r="Y48" s="2"/>
       <c r="Z48" s="2"/>
     </row>
-    <row r="49" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -2636,7 +2726,7 @@
       <c r="Y49" s="2"/>
       <c r="Z49" s="2"/>
     </row>
-    <row r="50" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -2664,7 +2754,7 @@
       <c r="Y50" s="2"/>
       <c r="Z50" s="2"/>
     </row>
-    <row r="51" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -2692,7 +2782,7 @@
       <c r="Y51" s="2"/>
       <c r="Z51" s="2"/>
     </row>
-    <row r="52" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -2720,7 +2810,7 @@
       <c r="Y52" s="2"/>
       <c r="Z52" s="2"/>
     </row>
-    <row r="53" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -2748,7 +2838,7 @@
       <c r="Y53" s="2"/>
       <c r="Z53" s="2"/>
     </row>
-    <row r="54" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -2776,7 +2866,7 @@
       <c r="Y54" s="2"/>
       <c r="Z54" s="2"/>
     </row>
-    <row r="55" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -2804,7 +2894,7 @@
       <c r="Y55" s="2"/>
       <c r="Z55" s="2"/>
     </row>
-    <row r="56" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -2832,7 +2922,7 @@
       <c r="Y56" s="2"/>
       <c r="Z56" s="2"/>
     </row>
-    <row r="57" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -2860,7 +2950,7 @@
       <c r="Y57" s="2"/>
       <c r="Z57" s="2"/>
     </row>
-    <row r="58" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -2888,7 +2978,7 @@
       <c r="Y58" s="2"/>
       <c r="Z58" s="2"/>
     </row>
-    <row r="59" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -2916,7 +3006,7 @@
       <c r="Y59" s="2"/>
       <c r="Z59" s="2"/>
     </row>
-    <row r="60" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -2944,7 +3034,7 @@
       <c r="Y60" s="2"/>
       <c r="Z60" s="2"/>
     </row>
-    <row r="61" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -2972,7 +3062,7 @@
       <c r="Y61" s="2"/>
       <c r="Z61" s="2"/>
     </row>
-    <row r="62" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -3000,7 +3090,7 @@
       <c r="Y62" s="2"/>
       <c r="Z62" s="2"/>
     </row>
-    <row r="63" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -3028,7 +3118,7 @@
       <c r="Y63" s="2"/>
       <c r="Z63" s="2"/>
     </row>
-    <row r="64" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -3056,7 +3146,7 @@
       <c r="Y64" s="2"/>
       <c r="Z64" s="2"/>
     </row>
-    <row r="65" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -3084,7 +3174,7 @@
       <c r="Y65" s="2"/>
       <c r="Z65" s="2"/>
     </row>
-    <row r="66" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -3112,7 +3202,7 @@
       <c r="Y66" s="2"/>
       <c r="Z66" s="2"/>
     </row>
-    <row r="67" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -3140,7 +3230,7 @@
       <c r="Y67" s="2"/>
       <c r="Z67" s="2"/>
     </row>
-    <row r="68" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -3168,7 +3258,7 @@
       <c r="Y68" s="2"/>
       <c r="Z68" s="2"/>
     </row>
-    <row r="69" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -3196,7 +3286,7 @@
       <c r="Y69" s="2"/>
       <c r="Z69" s="2"/>
     </row>
-    <row r="70" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -3224,7 +3314,7 @@
       <c r="Y70" s="2"/>
       <c r="Z70" s="2"/>
     </row>
-    <row r="71" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -3252,7 +3342,7 @@
       <c r="Y71" s="2"/>
       <c r="Z71" s="2"/>
     </row>
-    <row r="72" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -3280,7 +3370,7 @@
       <c r="Y72" s="2"/>
       <c r="Z72" s="2"/>
     </row>
-    <row r="73" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -3308,7 +3398,7 @@
       <c r="Y73" s="2"/>
       <c r="Z73" s="2"/>
     </row>
-    <row r="74" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -3336,7 +3426,7 @@
       <c r="Y74" s="2"/>
       <c r="Z74" s="2"/>
     </row>
-    <row r="75" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -3364,7 +3454,7 @@
       <c r="Y75" s="2"/>
       <c r="Z75" s="2"/>
     </row>
-    <row r="76" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -3392,7 +3482,7 @@
       <c r="Y76" s="2"/>
       <c r="Z76" s="2"/>
     </row>
-    <row r="77" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -3420,7 +3510,7 @@
       <c r="Y77" s="2"/>
       <c r="Z77" s="2"/>
     </row>
-    <row r="78" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -3448,7 +3538,7 @@
       <c r="Y78" s="2"/>
       <c r="Z78" s="2"/>
     </row>
-    <row r="79" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -3476,7 +3566,7 @@
       <c r="Y79" s="2"/>
       <c r="Z79" s="2"/>
     </row>
-    <row r="80" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -3504,7 +3594,7 @@
       <c r="Y80" s="2"/>
       <c r="Z80" s="2"/>
     </row>
-    <row r="81" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -3532,7 +3622,7 @@
       <c r="Y81" s="2"/>
       <c r="Z81" s="2"/>
     </row>
-    <row r="82" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -3560,7 +3650,7 @@
       <c r="Y82" s="2"/>
       <c r="Z82" s="2"/>
     </row>
-    <row r="83" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -3588,7 +3678,7 @@
       <c r="Y83" s="2"/>
       <c r="Z83" s="2"/>
     </row>
-    <row r="84" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -3616,7 +3706,7 @@
       <c r="Y84" s="2"/>
       <c r="Z84" s="2"/>
     </row>
-    <row r="85" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -3644,7 +3734,7 @@
       <c r="Y85" s="2"/>
       <c r="Z85" s="2"/>
     </row>
-    <row r="86" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -3672,7 +3762,7 @@
       <c r="Y86" s="2"/>
       <c r="Z86" s="2"/>
     </row>
-    <row r="87" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -3700,7 +3790,7 @@
       <c r="Y87" s="2"/>
       <c r="Z87" s="2"/>
     </row>
-    <row r="88" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -3728,7 +3818,7 @@
       <c r="Y88" s="2"/>
       <c r="Z88" s="2"/>
     </row>
-    <row r="89" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -3756,7 +3846,7 @@
       <c r="Y89" s="2"/>
       <c r="Z89" s="2"/>
     </row>
-    <row r="90" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -3784,7 +3874,7 @@
       <c r="Y90" s="2"/>
       <c r="Z90" s="2"/>
     </row>
-    <row r="91" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -3812,7 +3902,7 @@
       <c r="Y91" s="2"/>
       <c r="Z91" s="2"/>
     </row>
-    <row r="92" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -3840,7 +3930,7 @@
       <c r="Y92" s="2"/>
       <c r="Z92" s="2"/>
     </row>
-    <row r="93" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -3868,7 +3958,7 @@
       <c r="Y93" s="2"/>
       <c r="Z93" s="2"/>
     </row>
-    <row r="94" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -3896,7 +3986,7 @@
       <c r="Y94" s="2"/>
       <c r="Z94" s="2"/>
     </row>
-    <row r="95" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -3924,7 +4014,7 @@
       <c r="Y95" s="2"/>
       <c r="Z95" s="2"/>
     </row>
-    <row r="96" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -3952,7 +4042,7 @@
       <c r="Y96" s="2"/>
       <c r="Z96" s="2"/>
     </row>
-    <row r="97" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -3980,7 +4070,7 @@
       <c r="Y97" s="2"/>
       <c r="Z97" s="2"/>
     </row>
-    <row r="98" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -4008,7 +4098,7 @@
       <c r="Y98" s="2"/>
       <c r="Z98" s="2"/>
     </row>
-    <row r="99" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -4036,7 +4126,7 @@
       <c r="Y99" s="2"/>
       <c r="Z99" s="2"/>
     </row>
-    <row r="100" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
